--- a/光伏配储项目/电价数据/2026/谷饶站.xlsx
+++ b/光伏配储项目/电价数据/2026/谷饶站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.33439</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.6286799999999999</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.3433</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.36018</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.33733</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.37034</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.32499</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.32639</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.32596</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.31789</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.32223</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.31704</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.31658</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.3152</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.3142799999999999</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.31177</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.31496</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.3132799999999999</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.31404</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.31395</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.32177</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.31571</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.32272</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.32166</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.32476</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.32456</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.32443</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.31371</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.31363</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30863</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.3421</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.33338</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.31226</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.32082</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.31357</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.31374</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.27516</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.30367</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.25674</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.28459</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.2743</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.28726</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.33218</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.34037</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.31081</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.07379999999999999</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.49406</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.21304</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.17152</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.26618</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.25281</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.25742</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.24209</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.4189</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.32016</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.38595</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.29662</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.31255</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.32439</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.28166</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.30824</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.32964</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.32866</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.51419</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.52024</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.6185900000000001</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.98968</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.3661</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.38947</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.39012</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.3875</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.5630700000000001</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.71637</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.44761</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.0794</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.22887</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.96175</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.90215</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.03053</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.14382</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.42516</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.5938600000000001</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.62602</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.2047</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.70317</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.6774600000000001</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.6351599999999999</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.60605</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.4408</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.41007</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40412</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.36954</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.37559</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.62076</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.29674</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.72809</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.49423</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.7443500000000001</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.4725</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.48291</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.47733</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.47832</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.46408</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.38875</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.44815</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37025</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.32637</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33357</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.34043</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.32659</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.32679</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.32313</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.31991</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.33855</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.38159</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.37254</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.38829</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34379</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.33835</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.36538</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.45631</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.34517</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35443</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.36711</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.31746</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30385</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.2969</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.42854</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.45071</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.65738</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.6183</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.7639400000000001</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.29594</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.32378</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.32782</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.30203</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.3257</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.5582699999999999</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.59113</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.4882</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.40523</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.36283</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.34476</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.61848</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.38142</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.37147</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.98456</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.59245</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>1.10381</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.52278</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.48614</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.04904</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.84558</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.1664</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.05203</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.21266</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.00165</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.03659</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.8405900000000001</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.13002</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.8577</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.9331900000000001</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.8246100000000001</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.0005</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.84238</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.59644</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.43962</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.77539</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.76918</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.43968</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42039</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.43443</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33106</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35087</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33352</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.48814</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.4702</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.45406</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.36122</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.42995</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40245</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.35864</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38123</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.3742</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.35692</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.41351</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.42673</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33279</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.3632</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.38486</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.35917</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36056</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35465</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34613</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.33449</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.34101</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.36778</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.38276</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.45348</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.43439</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.42411</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34507</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.38571</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.34897</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36719</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34585</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.15477</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.19595</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.26831</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.3454100000000001</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.35906</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.11031</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.73239</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.6118400000000001</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.34837</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.59788</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.7582899999999999</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.7564</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.81202</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.76217</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.72538</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.74124</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.76832</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.8204400000000001</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.5154099999999999</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.54276</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.79195</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.76202</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.6993200000000001</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>1.00627</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.50124</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>1.29601</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.85397</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.48384</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.45819</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.51266</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.53299</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.7043400000000001</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.75219</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.7402000000000001</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.65816</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.5948300000000001</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.70508</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.5274800000000001</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.5214</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.74327</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>1.11197</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.87664</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.41325</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.5239199999999999</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.6726799999999999</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.56999</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.7364299999999999</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.95565</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>1.15863</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.75398</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.72815</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>1.15634</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.59217</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.54437</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.64781</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.43207</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.44795</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39259</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36193</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.3464100000000001</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34065</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.46023</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.44377</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.40568</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.37438</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.37485</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.36961</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.35535</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.36901</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.36792</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.35227</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.41025</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.35425</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34466</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.35632</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33492</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33283</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33001</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33116</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.34832</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33575</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.34183</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.37039</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.36893</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34658</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.36407</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34188</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.38935</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.39963</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.4216</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35732</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.44416</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.37557</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.3506</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.32806</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.48452</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.35607</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.35423</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.4192</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.18329</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.4827</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.4666</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.37738</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.70285</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.29385</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.78377</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.35712</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.33369</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.32409</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.38936</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>1.29162</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.34589</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31757</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34525</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.92571</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.6235599999999999</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.59348</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>1.25488</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.37812</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.49686</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1.04963</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.61165</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>1.3978</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.95255</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45064</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.7450399999999999</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.48192</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.82468</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.95596</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>1.26938</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.88685</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.6674</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.93198</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.91261</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50246</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.7235499999999999</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.66706</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.6626599999999999</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.63021</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.46851</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.46338</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34331</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.33927</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32137</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.31922</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.3121</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31572</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31315</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29118</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.36921</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.37359</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.37325</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35387</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32791</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32762</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31581</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31825</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.3168</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31196</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31334</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.3182</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31579</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30997</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30936</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31453</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31935</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31975</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.30799</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.32057</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.3443</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.30044</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.31905</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31393</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.33334</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31883</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.28948</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.29327</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.31979</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.31786</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.31453</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.14353</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.31569</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.02565</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.30383</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.29867</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.29475</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.31674</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.32224</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.30581</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.40642</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.5781900000000001</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.26505</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.25685</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.23961</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.10445</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.30731</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.27054</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.02936</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26348</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29737</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29978</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30065</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30484</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.33662</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.3469</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.33845</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34783</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.34857</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.36224</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.36646</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.42801</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35599</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.36728</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.36194</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.42154</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.34237</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35158</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34281</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.31814</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.3374</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.31337</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.30301</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.24644</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.25199</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.21326</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.30294</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.28974</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.32824</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.19532</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.24548</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.13385</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.25167</v>
+      </c>
+      <c r="O122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.31804</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.28977</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.30587</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.1579</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.25045</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.21815</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.19622</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.23767</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.17817</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.30617</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.25159</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.27273</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.32286</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.20506</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.26845</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10651</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04586</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04482999999999999</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.32224</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01009</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20634</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04933</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.27562</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.19405</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.32035</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.01108</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.06049</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05869</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34389</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.33764</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.32553</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.34081</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.3163</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.30285</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.24632</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.30961</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.35748</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.32693</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31933</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28083</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29728</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.39266</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37354</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.41805</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.43929</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41843</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41526</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.35098</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78367</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86287</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.2962</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88749</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18707</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87037</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.65724</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33083</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.0329</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7909700000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.57347</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729600000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7775299999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49314</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39866</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39987</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20698</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62183</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.43581</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41418</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.32874</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39297</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.35371</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.37806</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.38823</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.39919</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.32431</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.37491</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.32826</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.32593</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.32267</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.31743</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44386</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.32118</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.36463</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.3238</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.44851</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.32477</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.51874</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.58862</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.8286100000000001</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.78459</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.29295</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.44352</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.62621</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.14018</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.41263</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.3669</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87501</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.32845</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.32254</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.22741</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.30627</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.26683</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.51012</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>1.20151</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>1.03127</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.4382</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.39519</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32335</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.30532</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.28592</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31593</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29353</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29592</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.30787</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.29525</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.30553</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.18301</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.26367</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.26345</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.27802</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.26312</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.28219</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.32517</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.29311</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.31111</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.3013</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.29426</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.30521</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.30554</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.3096</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.30597</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.29243</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.32433</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.7063700000000001</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.30915</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.32838</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.32094</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.3168</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.30544</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.30826</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.30958</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.30826</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.30966</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.29461</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.29944</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.30354</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.30048</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.29694</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.2813</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.29618</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.30086</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.29866</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.29832</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.29898</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.29875</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.29925</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.29666</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.26527</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.23313</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.29253</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.26271</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.30626</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.30845</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30377</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30374</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.24663</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31217</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.35281</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.29108</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.25594</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30418</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.38297</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.37923</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>1.14627</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.45149</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.8700800000000001</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.24504</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.1758</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.25744</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29888</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.28046</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.24113</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.26597</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.26797</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.8730599999999999</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.96537</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.74274</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.69437</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.8030499999999999</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.7521</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.64054</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.73542</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>1.22515</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.8729199999999999</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.79618</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.90222</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.8691599999999999</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.26074</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.26329</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.2184</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.26001</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.24649</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.26173</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.26324</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.23626</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.25226</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.25726</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.25594</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.24055</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.26021</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.26444</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.27347</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.27047</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.26107</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.28468</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.25081</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.36555</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.28045</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.6121</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.24124</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.26472</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.47743</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.24933</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.24594</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.24917</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.57345</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.34959</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F126" t="n">
+        <v>1.35451</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.9233</v>
+      </c>
+      <c r="H126" t="n">
+        <v>1.24335</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.59536</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.57408</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.6746</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.70274</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.3276</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.39463</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.5495800000000001</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41384</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.25938</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.2704</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.49287</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.54796</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.2992</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.41809</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.34904</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.36066</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.4816</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.32581</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.34944</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.49442</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.38416</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.31455</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.25566</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.49252</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.35793</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.7500800000000001</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.33393</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.38669</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.57492</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.6115</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.34451</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.34839</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.33523</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.7607999999999999</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.38871</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.56809</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.48419</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.22381</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.27357</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.12524</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.23231</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.26377</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.28539</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.3007</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.33847</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.5376799999999999</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.26938</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.26042</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.6030599999999999</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.54571</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.39244</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.5511</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.38268</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.36975</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.72199</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.34672</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.6369400000000001</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.38769</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.30167</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.29778</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.29353</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.29855</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.2822</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.24695</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.30503</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.28305</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.25592</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.29382</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.28864</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.39843</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.26585</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.46707</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.28013</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.31003</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.30494</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.2722</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.30777</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.28695</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.24632</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.28313</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.22257</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.24877</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.23283</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.22486</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.14085</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.30564</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.1725</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.19098</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.16493</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.18816</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.13975</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.21157</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.23092</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.2287</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.26419</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.26056</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.42033</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.40328</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.59257</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.62178</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.25639</v>
+      </c>
+      <c r="W127" t="n">
+        <v>-0.02432</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.49394</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.19285</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-0.02791</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.44458</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.43025</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.1661</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.24389</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.48892</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.51673</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.25669</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.1451</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.34278</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.37929</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.25384</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.36566</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.16684</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.2458</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.23085</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.24043</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.29059</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.25331</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.28289</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.24829</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.24555</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.23616</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.24842</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.25533</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.28268</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.26568</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26288</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.26689</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.31597</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.27506</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.30379</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.35495</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.29829</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.31076</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.32735</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.30343</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.31725</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.30619</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.29782</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.30325</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.28311</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.28492</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.3002</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.30532</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.30712</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.30849</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.29415</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.32676</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.32881</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.32262</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.32873</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.31974</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.31333</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.32514</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.37939</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.50756</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.48232</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.4331</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.41958</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.28631</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.28861</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.25183</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.28309</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.29077</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.31134</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.33873</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.30706</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.30547</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.30608</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.30062</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.30299</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.30338</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.30447</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.30302</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.30498</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.30446</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.30016</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.29737</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.29698</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.29663</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.29544</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.29703</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.29544</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.30173</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.30442</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.29768</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.30295</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.30162</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.30216</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.29226</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.30235</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.29555</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.32206</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.30901</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.33141</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28266</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.3095</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31813</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.3034</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28524</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.30896</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.28354</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.45667</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.30236</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.28708</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.29704</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.29193</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27964</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29946</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.29761</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31204</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31491</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.29893</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.29996</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30538</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29477</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.31163</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.25246</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.2952</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.2878500000000001</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.30536</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.29059</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28941</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.29686</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.32313</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.32369</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.31645</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.30925</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.32827</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.36469</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.32067</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.3149</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.31375</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.31906</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.35647</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.41003</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.28316</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.34637</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.32834</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.31856</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.31264</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.30898</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.34543</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.31233</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.31209</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.32178</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.31086</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.31682</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.29058</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.30624</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.30569</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.30251</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.30303</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.32009</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.30962</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.30373</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.33308</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.31753</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.31325</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.30533</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.29471</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.28835</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.29352</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.29511</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.2988</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.30075</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.3176</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.29573</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.29671</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.29653</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.31382</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.30928</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.29456</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.31059</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.3061</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.2956</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.29728</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.29729</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.2918</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.33931</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31106</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.31506</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.30956</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.29674</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.30558</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.38272</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.88367</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.39766</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.57957</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.37685</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.4524</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.49196</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.37151</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.41068</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.45801</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.37382</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.40674</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.39344</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.49991</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.27786</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.32486</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.31108</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.39844</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.28363</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.34959</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.36441</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.60741</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.47177</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.39655</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.41758</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.39847</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.38396</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.48934</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.3962</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.38618</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.40198</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.36743</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.41014</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.38451</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.35425</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.33353</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.39028</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.35986</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.34474</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.52762</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.42454</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.4070299999999999</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.31543</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.4203</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.6993400000000001</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.38522</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.29543</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.34694</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.3185</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.34527</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.47564</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.20392</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.33493</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.3386</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.28987</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.25203</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.28663</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.19303</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.32431</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.30352</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.38524</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.29333</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.28181</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.28321</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.2834</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.20246</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.19454</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.27979</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.27879</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.27584</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.27944</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.27951</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.27538</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.19638</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.29608</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.19371</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.15824</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.23744</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.29082</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.29399</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.26388</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.19344</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.19912</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.31599</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.20611</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.17154</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.16278</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.24177</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.25549</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.31538</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.32666</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.37346</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.41577</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.32502</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.38235</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32779</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32725</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32719</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.32624</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.32646</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.31081</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.32102</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.32999</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.30129</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32422</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.2651</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.28813</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.29709</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.28276</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.29362</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.29512</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.32131</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.32348</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.3248</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.28259</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.26945</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32164</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32238</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.37487</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.42317</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.43831</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.34692</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.33831</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.32899</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.32365</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.34087</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.32039</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.30102</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.27017</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.28832</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.28561</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.31699</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.29624</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.33732</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.32923</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.27615</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.33042</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.28783</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.33185</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.31677</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.29166</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.3538</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.25625</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.34588</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.28223</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.34833</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.31783</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.24669</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.32201</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.23736</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.32161</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.29369</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.32122</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.32022</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.32124</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.32219</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.32166</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.32087</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.2825</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.32022</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.31707</v>
+      </c>
+      <c r="L131" t="n">
+        <v>-0.00679</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.31786</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.29056</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.28712</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.27529</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.31087</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.28697</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.28536</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.29521</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.28439</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.31042</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.2853</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.28662</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.27473</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.31587</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.28549</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.29126</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.29077</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.30715</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.28193</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.27549</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.28569</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.29407</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.27549</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.28598</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.27142</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.30025</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.30736</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.31661</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.30151</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31195</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.30616</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31025</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.30692</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.3053</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32899</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31792</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37009</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32535</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31814</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.30725</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.35824</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32119</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32819</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32183</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32299</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.31845</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32009</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32169</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.30403</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.32174</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.32528</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.32553</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.3241</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.33045</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.34042</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.32088</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.3216</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.32662</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.31651</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.32959</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.33217</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.32858</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.32094</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.32695</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.32611</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.32782</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.38277</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.34662</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.52995</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.48326</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.32381</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.20971</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.34459</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.33214</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.32119</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.33702</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.31045</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.29793</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.38198</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.34712</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.32411</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.33288</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.33003</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.32969</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.33286</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.32894</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.31637</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.32981</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.32367</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.31353</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.32696</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.32291</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.31253</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.33064</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.31844</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.28626</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.32961</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.32735</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.31056</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.33671</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.35072</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.3274</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.32731</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.32202</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.32271</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.32875</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.30849</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.41023</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.31742</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32249</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.31711</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.32055</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.31864</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.32501</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.3315</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.32819</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.31375</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.3176</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.32599</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.32174</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.32183</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.31881</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.32095</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.33757</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.32574</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.32781</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.32947</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.32757</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.33319</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33734</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.35145</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.40207</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.36836</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.34267</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33463</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.38263</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.34205</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.36354</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.42407</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.50175</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.5529700000000001</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.52288</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.56529</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.33724</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.69501</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.34673</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.40021</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.3689</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.44487</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.38614</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.40434</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.3427</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.3264</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.32176</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.34578</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.31801</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.31544</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.33203</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.3435</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.32277</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.31856</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.32345</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.32186</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.32293</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.36557</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.33435</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.32926</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.35891</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.31335</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.31148</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.31273</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.31152</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.29032</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.30594</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.31351</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.29764</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.28652</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.30115</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.30267</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.3141600000000001</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.31533</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.31534</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.31587</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.45078</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.39186</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.42578</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.42212</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.44677</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.48111</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.5794</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.4054</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.31752</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.32543</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.33452</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.33041</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.35308</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.44231</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.38253</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.36229</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.32258</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.35115</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.34569</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.4002</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.66826</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.40707</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.6602899999999999</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.39661</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.48314</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.34706</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.36429</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.34454</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33961</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.3395</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33539</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.33544</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.32227</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.46266</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35162</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.34921</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.32634</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.33824</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.33735</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.34821</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33467</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.33647</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.34051</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.33939</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.32592</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.33679</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.33434</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.34352</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.34576</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.34844</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.43686</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.33027</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.35179</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.34684</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.33338</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.34105</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.60115</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.50451</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6433300000000001</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.33699</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.32131</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.32443</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.32006</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.32473</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.32416</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.32429</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.32187</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.40533</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.39526</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.38699</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.31524</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.27125</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.28981</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.29406</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.31423</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.31008</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.31554</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.30656</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.33105</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.32785</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.33683</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.00741</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.27818</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.28581</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.33072</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.33683</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.27867</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.28575</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.29339</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.33225</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.32602</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.48971</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.36126</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.37024</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.32423</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.35748</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35091</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.32599</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.32287</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.32817</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.3342</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.5135599999999999</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.37162</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.34658</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.37515</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.58509</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.39046</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.3797</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.42124</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.39158</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.42951</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.42714</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.42427</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.34685</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.34784</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.32262</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.32931</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.33751</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.3107</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32559</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.32503</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.30392</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.31186</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.31004</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.31444</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.41399</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.40063</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.37867</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.32554</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.26809</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.39343</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.38829</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41319</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.37889</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.5037</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.34833</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.34507</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.3747799999999999</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.37972</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.36621</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.35203</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37835</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.33235</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.33157</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.33256</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.26389</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.31204</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.23684</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.24862</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.24366</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.33375</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.2301</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.31505</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.29457</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.27968</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.25959</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.29615</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.23611</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.17107</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.00533</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.27376</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.00199</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.00239</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.1713</v>
+      </c>
+      <c r="O135" t="n">
+        <v>-0.00874</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.20341</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.32227</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.17011</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.00137</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.16051</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.16513</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.19926</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.16272</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.16548</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.16824</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.0005600000000000001</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.17101</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.00041</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>-0.02414</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.18209</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.18498</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.15285</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.28419</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>-0.02964</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.32206</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.27105</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.30035</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.28165</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.17395</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28919</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.31389</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.26306</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.31727</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.3058</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.12417</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.41401</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.32333</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.34599</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.33936</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.32186</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.29806</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.33514</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.34437</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.33278</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.3356</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.37045</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.33483</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.31638</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.31373</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.32406</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.32397</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.30361</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.35208</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.34133</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.30534</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.3232</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.33151</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.33893</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.37017</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.25362</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.30195</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.31903</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.3278</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.33073</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.32359</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.32792</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.32343</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.22303</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.32996</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.25485</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.24872</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.25757</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.29493</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.27187</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.27058</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.22289</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.22848</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.27209</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.21535</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.28423</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.21434</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.25363</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.23085</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.33569</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.30509</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.29333</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.2857</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.27443</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.04755</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.1876</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.18459</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.26749</v>
+      </c>
+      <c r="L136" t="n">
+        <v>-0.008160000000000001</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.20394</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.22453</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.2163</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.0361</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-0.01945</v>
+      </c>
+      <c r="R136" t="n">
+        <v>-0.00591</v>
+      </c>
+      <c r="S136" t="n">
+        <v>-0.00592</v>
+      </c>
+      <c r="T136" t="n">
+        <v>-0.00641</v>
+      </c>
+      <c r="U136" t="n">
+        <v>-0.00641</v>
+      </c>
+      <c r="V136" t="n">
+        <v>-0.00612</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.19861</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-0.01986</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>-0.00641</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>-0.00637</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.17816</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>-0.01945</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>-0.01944</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.30515</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>-0.00501</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>-0.00805</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.24502</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.03189</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.0068</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00036</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.24361</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02204</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.00294</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04298</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04089</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04861</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04827</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02936</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04383</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04941</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.02487</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.30141</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04915</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.02284</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.05521</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.02938</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.25278</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.29614</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.32998</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.29522</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.3021</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>-0.00527</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.30027</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.31551</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.4535</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.42147</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.40695</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.28178</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.29536</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.31303</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.31534</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.29498</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.32843</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.32241</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.31636</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.33005</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.33186</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.32843</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.32497</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.31303</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.30509</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.29347</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.31331</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.29919</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.27073</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.34775</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.3319</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.30129</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.02219</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.2812</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.30657</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.28816</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.28094</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.17315</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.31863</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.16788</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.17229</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.16963</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-0.02887</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.16566</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.1544</v>
+      </c>
+      <c r="S137" t="n">
+        <v>-0.02817</v>
+      </c>
+      <c r="T137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V137" t="n">
+        <v>-0.03005</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-0.02798</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.00085</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.00278</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.006160000000000001</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.41536</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.19719</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.27798</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.32471</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>-0.02981</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.2391</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.32547</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.85823</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.86195</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32897</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.09185</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.00621</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.24959</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.31384</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.28076</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29565</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.2952</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.31775</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.48903</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.29906</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.29294</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.29232</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00166</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31657</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32073</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.31312</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06895</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.3075</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30259</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.30761</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30811</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25453</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29188</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.4751</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.31929</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32644</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32789</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33195</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.31586</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.32973</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32367</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.33357</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.59041</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.47323</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.36115</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.41356</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.6675</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.76418</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.37352</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.52704</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.41204</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.42857</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.65318</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.6514</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.6540199999999999</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.7193200000000001</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.35871</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.40473</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.36683</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32916</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.34894</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.30924</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.30907</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.3336</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.32094</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.42275</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.31042</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.29336</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.27346</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.35769</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.26695</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.19502</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.26081</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.25591</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.24916</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.2177</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.26326</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.20502</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.17073</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.20056</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.16515</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.16787</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-0.02941</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.16241</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.18573</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.2352</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.31577</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.28653</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.24409</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.25356</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.29836</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.25442</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.27702</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.30833</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.35572</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.32948</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.38106</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.30478</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.32878</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.29203</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.3111</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30738</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30856</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.25855</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31125</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30242</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30217</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.3467</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31685</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.33026</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31805</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.35868</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.34367</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.35252</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.35294</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.3559</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34613</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.34054</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.31826</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.32695</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.32762</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.33111</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.3627</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.34296</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.33287</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33581</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.33629</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.32145</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.39802</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.39865</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.48602</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.38364</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.493</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.31255</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.32167</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.32722</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.3149</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.30902</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.29721</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.29233</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.2929</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.3567</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.33326</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.33452</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.3317</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.33214</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32411</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.32011</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.31427</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.3141</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.32687</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.31614</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.31549</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.32243</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.31423</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.30311</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.30283</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.2952</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.29893</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.30111</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.30119</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.30756</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.30282</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.31323</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.30831</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.31395</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.3137</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.32004</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.30769</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.31744</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.31386</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.34408</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.5049399999999999</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.32241</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.3948</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.36296</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.32459</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.30994</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.31861</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.34392</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.33212</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.34376</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.37056</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.33658</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.36366</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.29633</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.33234</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32929</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33472</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.32029</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33363</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35773</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32261</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.32581</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33106</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.32871</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.33256</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.43266</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.40274</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.43102</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.24335</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.6634500000000001</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.68423</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.39842</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.43382</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.48208</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.59423</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.69647</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.40222</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.72151</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.40126</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.34466</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.42687</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.34898</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.34177</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.32508</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.35612</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.33882</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.32761</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.33372</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.32873</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.20189</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.32057</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.30878</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.31765</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.31884</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.3733</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.32665</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.32314</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.32292</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.31684</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.31572</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.34632</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.32093</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.31404</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.31884</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.31862</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.31562</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.31693</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.31653</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.3063</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.30184</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.30539</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.30073</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.29869</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.29471</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.32155</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.29474</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.30562</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.30991</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.30457</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.3374</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.31634</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.33195</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.33004</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.36153</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39097</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.34567</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35366</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.4346</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37966</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.34319</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.35548</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33609</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.35935</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.34857</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.33357</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.33949</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.3429</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.34233</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31629</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33671</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34153</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33802</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34417</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.33876</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.33819</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.34332</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.3479100000000001</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36659</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.34818</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.35963</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.35081</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.3471</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.37762</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.36527</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.6039099999999999</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.6415700000000001</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.56878</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.87371</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.66643</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.97519</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.56079</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.7400599999999999</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.6355299999999999</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.47634</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.93514</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.8414299999999999</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.46772</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.6561399999999999</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.58414</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.50758</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.33473</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.38129</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.3346</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.32501</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.32801</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.32064</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.32225</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.2844100000000001</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.33736</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.31102</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.32125</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.28521</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.2969</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.29062</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.30023</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.29116</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.30729</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.32427</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.31356</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.30237</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.30289</v>
+      </c>
+      <c r="S141" t="n">
+        <v>-0.0303</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.28924</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.29018</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.28482</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31485</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.32813</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.29221</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.28339</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.35743</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.33514</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.30584</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.3042</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.31411</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.30962</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.32165</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.32364</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.32686</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.33077</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.3618</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.39952</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.37905</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.27033</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.43127</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.51246</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.5639</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.34346</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.19977</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.52599</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.32911</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.29889</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.31862</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.43524</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.53498</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.34291</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.34678</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.31593</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.49004</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.58289</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.32696</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.46938</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.37133</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.35361</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.39702</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.3564</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.3448</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.36429</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.38316</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.8523999999999999</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>1.12553</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.33729</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35692</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.45936</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.46142</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.4061</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>1.73154</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.3234</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>1.05481</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.53487</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.44677</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.54404</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.7161900000000001</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.43564</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.5607799999999999</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.45279</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.47383</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.35846</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.35332</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.34479</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.3389</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.33883</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.32751</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.30988</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.32635</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34291</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.59787</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.38333</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.41069</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.39881</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.39337</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33587</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.35242</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.33568</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.33168</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.33428</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.33732</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.3327</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.33092</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.33295</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.33254</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.33213</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.33284</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.32799</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.32458</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.32663</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.32829</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.32482</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.3202</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.32626</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.32188</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.33321</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33061</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32569</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.32962</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33554</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.34065</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.33498</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.35628</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.35461</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.33871</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.35251</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.33077</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.34698</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.33317</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.33376</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.32919</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.31586</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.3223</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.30987</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.38538</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.31962</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.30473</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.28148</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.32324</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.37744</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.42445</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.30496</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32417</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.32625</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32328</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35391</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32354</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.35359</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.48111</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.58092</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>1.07503</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>1.76687</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.76109</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.47462</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.62258</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.5154</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.35229</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.52551</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>1.38729</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>1.72369</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.53755</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.57329</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.53487</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.49566</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.50922</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.62981</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.4818</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.3887</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.41439</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.45653</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.38446</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.34191</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.33666</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.33804</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.33913</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.33881</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34842</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.36798</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37211</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.35906</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35673</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.34285</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.3434700000000001</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.33991</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.34351</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.33659</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.34061</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34773</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.31911</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35586</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.32897</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33204</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32996</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.33045</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.33628</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33367</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.32539</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.33077</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.33319</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.33102</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.32975</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.3056</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31855</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.30944</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17609</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30458</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29572</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31173</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14575</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19864</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14628</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.28751</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04771</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12164</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33354</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22609</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.2602</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14379</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14536</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28364</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.18801</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.30732</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22683</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.29637</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.17499</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.3655</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30878</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.18522</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.31982</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.21631</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.37498</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.6705399999999999</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>1.1127</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.8915</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.62293</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.93928</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>1.56144</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.9643200000000001</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.76471</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.8102699999999999</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.5337999999999999</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.45544</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.8134</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.8577899999999999</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>1.50372</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.7605700000000001</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.7516</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.59041</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.68543</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.40773</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.44197</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.38868</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.3686</v>
       </c>
     </row>
   </sheetData>
